--- a/data/trans_camb/CAGE_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/CAGE_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,31</t>
+          <t>0,61; 3,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,58</t>
+          <t>0,06; 2,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,31</t>
+          <t>0,72; 4,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,0</t>
+          <t>-2,0; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,66</t>
+          <t>-0,36; 2,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 3,35</t>
+          <t>-0,24; 3,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,96</t>
+          <t>0,12; 1,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,07</t>
+          <t>0,14; 2,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,05</t>
+          <t>0,58; 3,08</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,13; —</t>
+          <t>-44,25; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,85; —</t>
+          <t>-65,77; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,9; —</t>
+          <t>56,26; —</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 3,31</t>
+          <t>-0,58; 3,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,57</t>
+          <t>-0,86; 1,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,87</t>
+          <t>-0,82; 2,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,07</t>
+          <t>-0,55; 1,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,81</t>
+          <t>-0,28; 1,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 4,47</t>
+          <t>0,32; 4,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,79</t>
+          <t>-0,27; 2,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 1,35</t>
+          <t>-0,29; 1,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,38</t>
+          <t>0,04; 2,2</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-58,84; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,81; —</t>
+          <t>-55,37; 1505,64</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,79</t>
+          <t>-0,19; 2,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,22</t>
+          <t>-0,41; 2,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 5,04</t>
+          <t>0,03; 4,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 4,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,91</t>
+          <t>-0,17; 1,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,14</t>
+          <t>-0,01; 2,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,29</t>
+          <t>0,25; 4,57</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 913,01</t>
+          <t>-28,57; 728,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-46,96; 731,52</t>
+          <t>-45,87; 807,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 1502,42</t>
+          <t>-35,98; 982,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,02; 696,75</t>
+          <t>-30,46; 765,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,64; 718,8</t>
+          <t>-28,76; 943,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 1579,85</t>
+          <t>-23,57; 1300,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,05</t>
+          <t>-0,11; 2,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,4</t>
+          <t>-0,54; 1,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,93</t>
+          <t>0,21; 3,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,13</t>
+          <t>-0,99; 0,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,57</t>
+          <t>-0,65; 0,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,13</t>
+          <t>-0,74; 1,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,15</t>
+          <t>-0,23; 1,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,83</t>
+          <t>-0,4; 0,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,31</t>
+          <t>-0,22; 2,43</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 295,72</t>
+          <t>-9,95; 298,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,82; 230,18</t>
+          <t>-39,37; 216,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,09; 550,72</t>
+          <t>4,09; 510,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,02; 219,37</t>
+          <t>-23,51; 224,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-43,34; 174,83</t>
+          <t>-42,79; 164,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 354,53</t>
+          <t>-25,82; 379,79</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,21</t>
+          <t>-0,97; 2,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,75</t>
+          <t>-1,17; 1,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,65</t>
+          <t>-0,11; 4,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,26</t>
+          <t>-1,84; 0,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,12</t>
+          <t>-1,86; 0,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 4,16</t>
+          <t>-0,11; 4,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,81</t>
+          <t>-0,92; 0,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,67</t>
+          <t>-1,0; 0,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,84</t>
+          <t>0,69; 4,0</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 535,61</t>
+          <t>-59,44; 493,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-71,44; 536,95</t>
+          <t>-67,0; 558,46</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 1359,94</t>
+          <t>-34,07; 1229,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 2032,35</t>
+          <t>-52,51; 2051,86</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-61,14; 188,5</t>
+          <t>-67,12; 196,95</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-69,79; 170,89</t>
+          <t>-72,91; 160,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>29,37; 758,89</t>
+          <t>37,17; 993,6</t>
         </is>
       </c>
     </row>
@@ -1757,37 +1757,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,86</t>
+          <t>0,55; 4,77</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,74</t>
+          <t>0,31; 4,03</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,0</t>
+          <t>-1,86; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,33</t>
+          <t>-0,16; 0,31</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 0,8</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 9,33</t>
+          <t>-0,16; 9,19</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,97</t>
+          <t>0,07; 1,01</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 4,98</t>
+          <t>-0,2; 4,78</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-52,75; —</t>
+          <t>-33,95; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5,5; —</t>
+          <t>-23,58; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1973,22 +1973,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,77</t>
+          <t>0,51; 1,74</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,19</t>
+          <t>0,1; 1,21</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,46</t>
+          <t>0,71; 2,38</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,08</t>
+          <t>-0,41; 0,09</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1998,22 +1998,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,83</t>
+          <t>0,22; 1,78</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,82</t>
+          <t>0,18; 0,8</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,76</t>
+          <t>0,11; 0,75</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,05</t>
+          <t>0,68; 1,98</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>57,7; 311,86</t>
+          <t>40,17; 292,43</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>12,03; 202,03</t>
+          <t>7,94; 199,33</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>73,86; 420,12</t>
+          <t>70,65; 402,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-88,27; 82,36</t>
+          <t>-87,3; 95,8</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-33,98; 350,61</t>
+          <t>-36,96; 369,44</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>39,56; 1190,0</t>
+          <t>47,95; 1096,63</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,14; 200,56</t>
+          <t>26,28; 197,1</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>16,04; 178,93</t>
+          <t>13,23; 184,1</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>108,18; 461,25</t>
+          <t>101,97; 445,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/CAGE_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/CAGE_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,07</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>1,97</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,58</t>
+          <t>0,63; 3,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,97</t>
+          <t>0,05; 2,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,31</t>
+          <t>1,09; 5,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,0</t>
+          <t>-1,63; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,73</t>
+          <t>-0,38; 2,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,35</t>
+          <t>-0,32; 2,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,95</t>
+          <t>0,18; 2,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,1</t>
+          <t>0,12; 2,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,08</t>
+          <t>0,82; 3,66</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1062,2%</t>
+          <t>1338,08%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>281,4%</t>
+          <t>264,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>672,29%</t>
+          <t>803,78%</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,25; —</t>
+          <t>-44,87; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,77; —</t>
+          <t>-49,13; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>56,26; —</t>
+          <t>60,21; —</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,28</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,07</t>
+          <t>-0,57; 2,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,44</t>
+          <t>-1,09; 1,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,0</t>
+          <t>-0,8; 2,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,06</t>
+          <t>-0,56; 1,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,95</t>
+          <t>-0,46; 1,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,58</t>
+          <t>0,53; 5,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,05</t>
+          <t>-0,3; 1,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,32</t>
+          <t>-0,3; 1,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,2</t>
+          <t>0,28; 2,84</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>105,89%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>662,43%</t>
+          <t>816,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>216,22%</t>
+          <t>305,7%</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,84; —</t>
+          <t>-71,08; 897,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,37; 1505,64</t>
+          <t>-20,28; —</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>2,65</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>2,25</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,83</t>
+          <t>-0,18; 2,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 2,51</t>
+          <t>-0,47; 2,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,72</t>
+          <t>0,43; 6,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,27</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,93</t>
+          <t>-0,17; 1,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,19</t>
+          <t>-0,09; 2,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 4,57</t>
+          <t>0,4; 5,26</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>235,52%</t>
+          <t>315,55%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>268,89%</t>
+          <t>351,86%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,57; 728,32</t>
+          <t>-36,53; 741,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,87; 807,61</t>
+          <t>-50,04; 571,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 982,38</t>
+          <t>-8,89; 1424,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,46; 765,47</t>
+          <t>-43,43; 642,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 943,84</t>
+          <t>-32,14; 815,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 1300,17</t>
+          <t>9,94; 1639,34</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,01</t>
+          <t>-0,05; 2,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,51</t>
+          <t>-0,55; 1,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,89</t>
+          <t>0,04; 3,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,13</t>
+          <t>-0,95; 0,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,54</t>
+          <t>-0,68; 0,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,07</t>
+          <t>0,06; 5,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,12</t>
+          <t>-0,14; 1,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,87</t>
+          <t>-0,42; 0,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 2,43</t>
+          <t>0,41; 2,81</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>154,83%</t>
+          <t>119,31%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>444,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>115,31%</t>
+          <t>173,8%</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 298,97</t>
+          <t>-10,2; 289,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,37; 216,41</t>
+          <t>-39,19; 229,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,09; 510,4</t>
+          <t>-7,12; 406,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 224,21</t>
+          <t>-19,49; 246,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,79; 164,67</t>
+          <t>-41,26; 154,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 379,79</t>
+          <t>19,86; 452,82</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>2,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 2,1</t>
+          <t>-1,0; 2,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,71</t>
+          <t>-1,2; 1,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 4,91</t>
+          <t>0,21; 5,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,22</t>
+          <t>-1,69; 0,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,09</t>
+          <t>-1,72; 0,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 4,03</t>
+          <t>-0,25; 3,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,78</t>
+          <t>-0,83; 0,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,58</t>
+          <t>-0,95; 0,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,0</t>
+          <t>0,55; 3,79</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>186,29%</t>
+          <t>208,54%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>212,3%</t>
+          <t>182,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>231,33%</t>
+          <t>239,26%</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-59,44; 493,58</t>
+          <t>-52,76; 714,86</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-67,0; 558,46</t>
+          <t>-67,03; 587,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,07; 1229,47</t>
+          <t>-14,34; 1550,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1672,29 +1672,29 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-52,51; 2051,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-67,12; 196,95</t>
+          <t>-62,27; 193,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-72,91; 160,29</t>
+          <t>-71,94; 162,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>37,17; 993,6</t>
+          <t>14,36; 834,47</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,75</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>0,91</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,77</t>
+          <t>0,49; 4,85</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,03</t>
+          <t>0,33; 3,78</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,0</t>
+          <t>-1,77; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,31</t>
+          <t>-0,16; 0,27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,01; 0,8</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 9,19</t>
+          <t>-0,16; 9,04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,01</t>
+          <t>0,06; 0,97</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,08</t>
+          <t>0,15; 1,19</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 4,78</t>
+          <t>-0,2; 5,13</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2151,56%</t>
+          <t>2057,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>667,79%</t>
+          <t>680,82%</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-33,95; —</t>
+          <t>-40,34; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-23,58; —</t>
+          <t>-14,05; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,68</t>
         </is>
       </c>
     </row>
@@ -1973,22 +1973,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,74</t>
+          <t>0,6; 1,77</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,21</t>
+          <t>0,12; 1,17</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,38</t>
+          <t>0,93; 2,62</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,09</t>
+          <t>-0,39; 0,08</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1998,22 +1998,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,78</t>
+          <t>0,74; 2,81</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,8</t>
+          <t>0,2; 0,84</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,75</t>
+          <t>0,14; 0,75</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,98</t>
+          <t>1,12; 2,38</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>191,56%</t>
+          <t>214,55%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>329,65%</t>
+          <t>527,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>252,54%</t>
+          <t>320,47%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>40,17; 292,43</t>
+          <t>52,89; 305,72</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7,94; 199,33</t>
+          <t>9,22; 202,3</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>70,65; 402,29</t>
+          <t>84,94; 441,97</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-87,3; 95,8</t>
+          <t>-87,96; 85,6</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 369,44</t>
+          <t>-30,91; 381,05</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>47,95; 1096,63</t>
+          <t>155,17; 1751,33</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,28; 197,1</t>
+          <t>27,13; 210,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>13,23; 184,1</t>
+          <t>21,3; 188,45</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>101,97; 445,33</t>
+          <t>166,5; 541,88</t>
         </is>
       </c>
     </row>
